--- a/new/da-DK/new.xlsx
+++ b/new/da-DK/new.xlsx
@@ -53,7 +53,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
